--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>105.7988284304955</v>
+        <v>17.19230961995552</v>
       </c>
       <c r="D2" t="n">
-        <v>102.7503842046862</v>
+        <v>16.69693743326151</v>
       </c>
       <c r="E2" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F2" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.82035366626178</v>
+        <v>12.64580747076754</v>
       </c>
       <c r="D3" t="n">
-        <v>73.58468272295329</v>
+        <v>11.95751094247991</v>
       </c>
       <c r="E3" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F3" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>90.37226362382012</v>
+        <v>14.68549283887077</v>
       </c>
       <c r="D4" t="n">
-        <v>88.85671348520192</v>
+        <v>14.43921594134531</v>
       </c>
       <c r="E4" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F4" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>78.30951492728563</v>
+        <v>12.72529617568392</v>
       </c>
       <c r="D5" t="n">
-        <v>74.10860623043982</v>
+        <v>12.04264851244647</v>
       </c>
       <c r="E5" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F5" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>84.9576952102465</v>
+        <v>13.80562547166506</v>
       </c>
       <c r="D6" t="n">
-        <v>81.08801094385478</v>
+        <v>13.1768017783764</v>
       </c>
       <c r="E6" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F6" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>82.39521163735384</v>
+        <v>13.38922189107</v>
       </c>
       <c r="D7" t="n">
-        <v>78.51751861395785</v>
+        <v>12.75909677476815</v>
       </c>
       <c r="E7" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F7" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>88.03746145569133</v>
+        <v>14.30608748654984</v>
       </c>
       <c r="D8" t="n">
-        <v>86.55248337149844</v>
+        <v>14.0647785478685</v>
       </c>
       <c r="E8" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F8" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>84.42030672257879</v>
+        <v>13.71829984241905</v>
       </c>
       <c r="D9" t="n">
-        <v>80.79229021204594</v>
+        <v>13.12874715945747</v>
       </c>
       <c r="E9" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F9" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>86.05702135066811</v>
+        <v>13.98426596948357</v>
       </c>
       <c r="D10" t="n">
-        <v>84.54007824528631</v>
+        <v>13.73776271485903</v>
       </c>
       <c r="E10" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F10" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>71.71285486619874</v>
+        <v>11.6533389157573</v>
       </c>
       <c r="D11" t="n">
-        <v>67.48524415997956</v>
+        <v>10.96635217599668</v>
       </c>
       <c r="E11" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F11" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>73.30669804038763</v>
+        <v>11.91233843156299</v>
       </c>
       <c r="D12" t="n">
-        <v>69.35554159145059</v>
+        <v>11.27027550861072</v>
       </c>
       <c r="E12" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F12" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>75.01758016044782</v>
+        <v>12.19035677607277</v>
       </c>
       <c r="D13" t="n">
-        <v>71.25977009831492</v>
+        <v>11.57971264097617</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F13" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>80.10714494638407</v>
+        <v>13.01741105378741</v>
       </c>
       <c r="D14" t="n">
-        <v>76.5933073904891</v>
+        <v>12.44641245095448</v>
       </c>
       <c r="E14" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F14" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>79.6562825541382</v>
+        <v>12.94414591504746</v>
       </c>
       <c r="D15" t="n">
-        <v>78.16837280686424</v>
+        <v>12.70236058111544</v>
       </c>
       <c r="E15" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F15" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.06318151526917</v>
+        <v>9.760266996231241</v>
       </c>
       <c r="D16" t="n">
-        <v>55.84259411356981</v>
+        <v>9.074421543455095</v>
       </c>
       <c r="E16" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F16" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>72.48073536367214</v>
+        <v>11.77811949659672</v>
       </c>
       <c r="D17" t="n">
-        <v>68.98024143965692</v>
+        <v>11.20928923394425</v>
       </c>
       <c r="E17" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F17" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.77609828861123</v>
+        <v>9.226115971899326</v>
       </c>
       <c r="D18" t="n">
-        <v>52.69986983561007</v>
+        <v>8.563728848286637</v>
       </c>
       <c r="E18" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F18" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>54.55505203932652</v>
+        <v>8.86519595639056</v>
       </c>
       <c r="D19" t="n">
-        <v>50.40700481360442</v>
+        <v>8.191138282210717</v>
       </c>
       <c r="E19" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F19" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>66.08212137068621</v>
+        <v>10.73834472273651</v>
       </c>
       <c r="D20" t="n">
-        <v>64.5651061772006</v>
+        <v>10.4918297537951</v>
       </c>
       <c r="E20" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F20" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>65.95645085317732</v>
+        <v>10.71792326364131</v>
       </c>
       <c r="D21" t="n">
-        <v>62.69905177029884</v>
+        <v>10.18859591267356</v>
       </c>
       <c r="E21" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F21" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>65.17032554847165</v>
+        <v>10.59017790162664</v>
       </c>
       <c r="D22" t="n">
-        <v>63.68047567783639</v>
+        <v>10.34807729764841</v>
       </c>
       <c r="E22" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F22" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>84.43930833665316</v>
+        <v>13.72138760470614</v>
       </c>
       <c r="D23" t="n">
-        <v>82.19795647473485</v>
+        <v>13.35716792714441</v>
       </c>
       <c r="E23" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F23" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>56.2814615861578</v>
+        <v>9.145737507750642</v>
       </c>
       <c r="D24" t="n">
-        <v>54.76998162172429</v>
+        <v>8.900122013530197</v>
       </c>
       <c r="E24" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F24" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>47.39823828058016</v>
+        <v>7.702213720594276</v>
       </c>
       <c r="D25" t="n">
-        <v>45.88334676601627</v>
+        <v>7.456043849477644</v>
       </c>
       <c r="E25" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F25" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>47.19726370883274</v>
+        <v>7.669555352685321</v>
       </c>
       <c r="D26" t="n">
-        <v>45.73347143928511</v>
+        <v>7.43168910888383</v>
       </c>
       <c r="E26" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F26" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>48.55342862021619</v>
+        <v>7.889932150785131</v>
       </c>
       <c r="D27" t="n">
-        <v>45.5555257125566</v>
+        <v>7.402772928290448</v>
       </c>
       <c r="E27" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F27" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>56.30091046340748</v>
+        <v>9.148897950303715</v>
       </c>
       <c r="D28" t="n">
-        <v>53.95728759449755</v>
+        <v>8.768059234105852</v>
       </c>
       <c r="E28" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F28" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>48.47700009400198</v>
+        <v>7.877512515275322</v>
       </c>
       <c r="D29" t="n">
-        <v>46.98218726423722</v>
+        <v>7.634605430438548</v>
       </c>
       <c r="E29" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F29" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>44.5611528865869</v>
+        <v>7.241187344070372</v>
       </c>
       <c r="D30" t="n">
-        <v>40.32946030258869</v>
+        <v>6.553537299170662</v>
       </c>
       <c r="E30" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F30" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>72.90508371706279</v>
+        <v>11.8470761040227</v>
       </c>
       <c r="D31" t="n">
-        <v>71.46022173260452</v>
+        <v>11.61228603154824</v>
       </c>
       <c r="E31" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F31" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>32.50855779273692</v>
+        <v>5.282640641319749</v>
       </c>
       <c r="D32" t="n">
-        <v>28.50241337351765</v>
+        <v>4.631642173196619</v>
       </c>
       <c r="E32" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F32" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>61.26316549296871</v>
+        <v>9.955264392607416</v>
       </c>
       <c r="D33" t="n">
-        <v>59.80198776042094</v>
+        <v>9.717823011068402</v>
       </c>
       <c r="E33" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F33" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>42.62317396524066</v>
+        <v>6.926265769351607</v>
       </c>
       <c r="D34" t="n">
-        <v>40.38827606559461</v>
+        <v>6.563094860659124</v>
       </c>
       <c r="E34" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F34" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>24.18178337817733</v>
+        <v>3.929539798953817</v>
       </c>
       <c r="D35" t="n">
-        <v>19.9463969123173</v>
+        <v>3.241289498251561</v>
       </c>
       <c r="E35" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F35" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>48.58646357023614</v>
+        <v>7.895300330163373</v>
       </c>
       <c r="D36" t="n">
-        <v>46.76844145669963</v>
+        <v>7.599871736713689</v>
       </c>
       <c r="E36" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F36" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>28.42874122362573</v>
+        <v>4.619670448839181</v>
       </c>
       <c r="D37" t="n">
-        <v>26.91358119020112</v>
+        <v>4.373456943407682</v>
       </c>
       <c r="E37" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F37" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>26.90657276799561</v>
+        <v>4.372318074799288</v>
       </c>
       <c r="D38" t="n">
-        <v>25.14464697625972</v>
+        <v>4.086005133642204</v>
       </c>
       <c r="E38" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F38" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>23.7058571586761</v>
+        <v>3.852201788284867</v>
       </c>
       <c r="D39" t="n">
-        <v>21.45416313960092</v>
+        <v>3.486301510185149</v>
       </c>
       <c r="E39" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F39" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>34.0385434687822</v>
+        <v>5.531263313677108</v>
       </c>
       <c r="D40" t="n">
-        <v>32.67447116100404</v>
+        <v>5.309601563663157</v>
       </c>
       <c r="E40" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F40" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>28.21948027449106</v>
+        <v>4.585665544604797</v>
       </c>
       <c r="D41" t="n">
-        <v>27.34916509692393</v>
+        <v>4.444239328250138</v>
       </c>
       <c r="E41" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F41" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>58.79394865478341</v>
+        <v>9.554016656402306</v>
       </c>
       <c r="D42" t="n">
-        <v>58.58751275819263</v>
+        <v>9.520470823206303</v>
       </c>
       <c r="E42" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F42" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>74.24832943330139</v>
+        <v>12.06535353291148</v>
       </c>
       <c r="D43" t="n">
-        <v>74.11031890188792</v>
+        <v>12.04292682155679</v>
       </c>
       <c r="E43" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F43" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>44.76382748344234</v>
+        <v>7.274121966059381</v>
       </c>
       <c r="D44" t="n">
-        <v>44.57271721411469</v>
+        <v>7.243066547293637</v>
       </c>
       <c r="E44" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F44" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>29.49239154411264</v>
+        <v>4.792513625918304</v>
       </c>
       <c r="D45" t="n">
-        <v>28.56536464143961</v>
+        <v>4.641871754233937</v>
       </c>
       <c r="E45" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F45" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>32.29172590690194</v>
+        <v>5.247405459871565</v>
       </c>
       <c r="D46" t="n">
-        <v>31.62569151898503</v>
+        <v>5.139174871835068</v>
       </c>
       <c r="E46" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F46" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>4.387213456990171</v>
+        <v>0.7129221867609028</v>
       </c>
       <c r="D47" t="n">
-        <v>2.557723417538187</v>
+        <v>0.4156300553499555</v>
       </c>
       <c r="E47" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F47" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>16.65952087707893</v>
+        <v>2.707172142525326</v>
       </c>
       <c r="D48" t="n">
-        <v>17.13139980634866</v>
+        <v>2.783852468531657</v>
       </c>
       <c r="E48" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F48" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>15.94855480513029</v>
+        <v>2.591640155833673</v>
       </c>
       <c r="D49" t="n">
-        <v>17.07204216882427</v>
+        <v>2.774206852433944</v>
       </c>
       <c r="E49" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F49" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>47.18342226755114</v>
+        <v>7.667306118477061</v>
       </c>
       <c r="D50" t="n">
-        <v>47.76442491509162</v>
+        <v>7.761719048702388</v>
       </c>
       <c r="E50" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F50" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>7.854574881081395</v>
+        <v>1.276368418175727</v>
       </c>
       <c r="D51" t="n">
-        <v>10.83042913916413</v>
+        <v>1.759944735114171</v>
       </c>
       <c r="E51" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F51" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>10.80176892039962</v>
+        <v>1.755287449564938</v>
       </c>
       <c r="D52" t="n">
-        <v>9.749318362240475</v>
+        <v>1.584264233864077</v>
       </c>
       <c r="E52" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F52" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>32.24017426589479</v>
+        <v>5.239028318207903</v>
       </c>
       <c r="D53" t="n">
-        <v>33.13037510520134</v>
+        <v>5.383685954595218</v>
       </c>
       <c r="E53" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F53" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>15.57478209628131</v>
+        <v>2.530902090645714</v>
       </c>
       <c r="D54" t="n">
-        <v>17.81666378105521</v>
+        <v>2.895207864421471</v>
       </c>
       <c r="E54" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F54" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>24.13013119081699</v>
+        <v>3.921146318507761</v>
       </c>
       <c r="D55" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="E55" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F55" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>45.50017972832394</v>
+        <v>7.393779205852641</v>
       </c>
       <c r="D56" t="n">
-        <v>46.60244190057811</v>
+        <v>7.572896808843943</v>
       </c>
       <c r="E56" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F56" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>39.2099942604589</v>
+        <v>6.371624067324571</v>
       </c>
       <c r="D57" t="n">
-        <v>40.68452694894492</v>
+        <v>6.611235629203549</v>
       </c>
       <c r="E57" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F57" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>10.22995511605704</v>
+        <v>1.66236770635927</v>
       </c>
       <c r="D58" t="n">
-        <v>14.35214387029999</v>
+        <v>2.332223378923748</v>
       </c>
       <c r="E58" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F58" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>20.94741902705702</v>
+        <v>3.403955591896765</v>
       </c>
       <c r="D59" t="n">
-        <v>20.45399010887112</v>
+        <v>3.323773392691557</v>
       </c>
       <c r="E59" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F59" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>15.20486968315009</v>
+        <v>2.47079132351189</v>
       </c>
       <c r="D60" t="n">
-        <v>18.46564585096403</v>
+        <v>3.000667450781655</v>
       </c>
       <c r="E60" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F60" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>3.223444632437926</v>
+        <v>0.523809752771163</v>
       </c>
       <c r="D61" t="n">
-        <v>4.740522748215651</v>
+        <v>0.7703349465850433</v>
       </c>
       <c r="E61" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F61" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>18.37995070007391</v>
+        <v>2.986741988762011</v>
       </c>
       <c r="D62" t="n">
-        <v>21.22498527679112</v>
+        <v>3.449060107478558</v>
       </c>
       <c r="E62" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F62" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>24.34319624287155</v>
+        <v>3.955769389466626</v>
       </c>
       <c r="D63" t="n">
-        <v>7.575160657366339</v>
+        <v>1.23096360682203</v>
       </c>
       <c r="E63" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F63" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>76.85300644482581</v>
+        <v>12.48861354728419</v>
       </c>
       <c r="D64" t="n">
-        <v>78.2352078022558</v>
+        <v>12.71322126786657</v>
       </c>
       <c r="E64" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F64" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>33.93490146513526</v>
+        <v>5.51442148808448</v>
       </c>
       <c r="D65" t="n">
-        <v>36.71500036856236</v>
+        <v>5.966187559891384</v>
       </c>
       <c r="E65" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F65" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>26.23620057643187</v>
+        <v>4.263382593670179</v>
       </c>
       <c r="D66" t="n">
-        <v>21.50581316760657</v>
+        <v>3.494694639736068</v>
       </c>
       <c r="E66" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F66" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>11.01620222307075</v>
+        <v>1.790132861248997</v>
       </c>
       <c r="D67" t="n">
-        <v>12.12264737409691</v>
+        <v>1.969930198290749</v>
       </c>
       <c r="E67" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F67" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>39.91362453756738</v>
+        <v>6.485963987354699</v>
       </c>
       <c r="D68" t="n">
-        <v>43.39694696435863</v>
+        <v>7.052003881708278</v>
       </c>
       <c r="E68" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F68" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>39.00132109260708</v>
+        <v>6.33771467754865</v>
       </c>
       <c r="D69" t="n">
-        <v>8.139410298049853</v>
+        <v>1.322654173433101</v>
       </c>
       <c r="E69" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F69" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>42.07100132517314</v>
+        <v>6.836537715340635</v>
       </c>
       <c r="D70" t="n">
-        <v>17.28117819273754</v>
+        <v>2.808191456319851</v>
       </c>
       <c r="E70" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F70" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>37.69795284233771</v>
+        <v>6.125917336879879</v>
       </c>
       <c r="D71" t="n">
-        <v>23.53160264027271</v>
+        <v>3.823885429044315</v>
       </c>
       <c r="E71" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F71" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>26.61620440752589</v>
+        <v>4.325133216222958</v>
       </c>
       <c r="D72" t="n">
-        <v>28.1334525968206</v>
+        <v>4.571686046983348</v>
       </c>
       <c r="E72" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F72" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>62.99626619340302</v>
+        <v>10.23689325642799</v>
       </c>
       <c r="D73" t="n">
-        <v>66.2696654227794</v>
+        <v>10.76882063120165</v>
       </c>
       <c r="E73" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F73" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>47.99980589798113</v>
+        <v>7.799968458421933</v>
       </c>
       <c r="D74" t="n">
-        <v>29.70269348055829</v>
+        <v>4.826687690590723</v>
       </c>
       <c r="E74" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F74" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>57.6336155154947</v>
+        <v>9.36546252126789</v>
       </c>
       <c r="D75" t="n">
-        <v>57.09787793253872</v>
+        <v>9.278405164037542</v>
       </c>
       <c r="E75" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F75" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>51.57260921908106</v>
+        <v>8.380548998100672</v>
       </c>
       <c r="D76" t="n">
-        <v>37.50333318519835</v>
+        <v>6.094291642594732</v>
       </c>
       <c r="E76" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F76" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>54.46768924612282</v>
+        <v>8.850999502494959</v>
       </c>
       <c r="D77" t="n">
-        <v>30.50567458349611</v>
+        <v>4.957172119818117</v>
       </c>
       <c r="E77" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F77" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>60.65746624322803</v>
+        <v>9.856838264524555</v>
       </c>
       <c r="D78" t="n">
-        <v>38.5903261638357</v>
+        <v>6.270928001623301</v>
       </c>
       <c r="E78" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F78" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>62.40213291451018</v>
+        <v>10.14034659860791</v>
       </c>
       <c r="D79" t="n">
-        <v>36.34556369077249</v>
+        <v>5.90615409975053</v>
       </c>
       <c r="E79" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F79" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>61.73414307583898</v>
+        <v>10.03179824982383</v>
       </c>
       <c r="D80" t="n">
-        <v>41.62030754331352</v>
+        <v>6.763299975788446</v>
       </c>
       <c r="E80" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F80" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>67.18061329483365</v>
+        <v>10.91684966041047</v>
       </c>
       <c r="D81" t="n">
-        <v>41.86287137786896</v>
+        <v>6.802716598903706</v>
       </c>
       <c r="E81" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F81" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>52.59541860132236</v>
+        <v>8.546755522714884</v>
       </c>
       <c r="D82" t="n">
-        <v>54.06643670540574</v>
+        <v>8.785795964628434</v>
       </c>
       <c r="E82" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F82" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>72.65221325901854</v>
+        <v>11.80598465459051</v>
       </c>
       <c r="D83" t="n">
-        <v>45.83606052492344</v>
+        <v>7.448359835300059</v>
       </c>
       <c r="E83" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F83" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>59.65320579255461</v>
+        <v>9.693645941290125</v>
       </c>
       <c r="D84" t="n">
-        <v>54.50637067760469</v>
+        <v>8.857285235110762</v>
       </c>
       <c r="E84" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F84" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>55.646394459878</v>
+        <v>9.042539099730174</v>
       </c>
       <c r="D85" t="n">
-        <v>57.15349322903794</v>
+        <v>9.287442649718665</v>
       </c>
       <c r="E85" t="n">
-        <v>23.72466392025888</v>
+        <v>3.855257887042068</v>
       </c>
       <c r="F85" t="n">
-        <v>23.61255308222347</v>
+        <v>3.837039875861315</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
